--- a/Data/EC/NIT-9009383962.xlsx
+++ b/Data/EC/NIT-9009383962.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{521114A4-3CBB-421B-9F3A-219D159BAC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF0169B0-B7BE-4F93-AC78-79D6C03C552B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{052DCD52-6CE4-482E-A847-23C0BD236CAB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CE189767-EDCC-4CCE-BD9B-E0DB07AFCE80}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="112">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -80,247 +80,265 @@
     <t>LUIS CARLOS PUCHE IZQUIERDO</t>
   </si>
   <si>
+    <t>2602</t>
+  </si>
+  <si>
+    <t>2601</t>
+  </si>
+  <si>
+    <t>2512</t>
+  </si>
+  <si>
+    <t>2511</t>
+  </si>
+  <si>
+    <t>2510</t>
+  </si>
+  <si>
+    <t>2509</t>
+  </si>
+  <si>
+    <t>2508</t>
+  </si>
+  <si>
+    <t>2507</t>
+  </si>
+  <si>
+    <t>2506</t>
+  </si>
+  <si>
+    <t>2505</t>
+  </si>
+  <si>
+    <t>2504</t>
+  </si>
+  <si>
+    <t>2503</t>
+  </si>
+  <si>
+    <t>2502</t>
+  </si>
+  <si>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
     <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>2306</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>2308</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2411</t>
-  </si>
-  <si>
-    <t>2412</t>
-  </si>
-  <si>
-    <t>2501</t>
-  </si>
-  <si>
-    <t>2502</t>
-  </si>
-  <si>
-    <t>2503</t>
-  </si>
-  <si>
-    <t>2504</t>
-  </si>
-  <si>
-    <t>2505</t>
-  </si>
-  <si>
-    <t>2506</t>
-  </si>
-  <si>
-    <t>2507</t>
-  </si>
-  <si>
-    <t>2508</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -364,7 +382,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,9 +437,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -434,7 +450,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -634,23 +652,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -678,10 +696,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -719,22 +737,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>426600</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>189350</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87C226C4-1A3D-EB1F-D080-645F69E71557}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F23C290B-049B-CB4F-CE0A-4BA62CE9FA56}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -756,7 +774,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="680600" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1085,27 +1103,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E991DE71-59FA-4C16-8D5D-F91D61406BF5}">
-  <dimension ref="B2:J103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F9FCF14-3489-4209-A3D3-D8816EAAE174}">
+  <dimension ref="B2:J109"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="16.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1114,7 +1132,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1125,7 +1143,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1136,7 +1154,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1147,10 +1165,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1"/>
-    <row r="7" spans="2:10">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1163,8 +1181,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1"/>
-    <row r="9" spans="2:10">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1179,15 +1197,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1"/>
-    <row r="11" spans="2:10">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>2603169</v>
+        <v>2790663</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1195,27 +1213,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1"/>
-    <row r="13" spans="2:10">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C13" s="5">
         <v>2</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F13" s="5">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1235,16 +1253,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1267,7 +1285,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1290,7 +1308,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1313,7 +1331,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1336,7 +1354,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1359,7 +1377,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1382,7 +1400,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1405,7 +1423,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1428,7 +1446,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1451,7 +1469,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1474,7 +1492,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1497,7 +1515,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1520,7 +1538,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1543,7 +1561,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1566,7 +1584,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1589,7 +1607,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1612,7 +1630,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1635,7 +1653,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1658,7 +1676,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1681,7 +1699,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1704,7 +1722,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1727,7 +1745,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +1768,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1773,7 +1791,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1796,7 +1814,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1819,7 +1837,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1842,7 +1860,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1865,7 +1883,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1888,7 +1906,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1911,7 +1929,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1934,7 +1952,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1957,7 +1975,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1980,7 +1998,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2003,7 +2021,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2026,7 +2044,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2049,7 +2067,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2072,7 +2090,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2095,7 +2113,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2118,7 +2136,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2141,7 +2159,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2164,7 +2182,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2187,7 +2205,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2210,7 +2228,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2233,7 +2251,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2256,7 +2274,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2279,7 +2297,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2302,7 +2320,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2325,7 +2343,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2348,7 +2366,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2371,7 +2389,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2394,7 +2412,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2417,7 +2435,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2440,7 +2458,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2463,7 +2481,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2486,7 +2504,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2509,7 +2527,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2532,7 +2550,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2555,7 +2573,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2578,7 +2596,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2601,7 +2619,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2624,7 +2642,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2647,7 +2665,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2670,7 +2688,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2693,7 +2711,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2716,7 +2734,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2739,7 +2757,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2762,7 +2780,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2785,7 +2803,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2808,7 +2826,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2831,7 +2849,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2854,7 +2872,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2877,7 +2895,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2900,7 +2918,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2923,7 +2941,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2946,7 +2964,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2969,7 +2987,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2992,7 +3010,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3015,7 +3033,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3038,7 +3056,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3061,7 +3079,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3084,7 +3102,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3107,57 +3125,195 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10">
-      <c r="B97" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C97" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D97" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="22" t="s">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B97" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="F97" s="24">
-        <v>31249</v>
-      </c>
-      <c r="G97" s="24">
-        <v>781242</v>
-      </c>
-      <c r="H97" s="25"/>
-      <c r="I97" s="25"/>
-      <c r="J97" s="26"/>
-    </row>
-    <row r="102" spans="2:10">
-      <c r="B102" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="C102" s="32"/>
-      <c r="H102" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1"/>
-    </row>
-    <row r="103" spans="2:10">
-      <c r="B103" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="C103" s="32"/>
-      <c r="H103" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
+      <c r="F97" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G97" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H97" s="19"/>
+      <c r="I97" s="19"/>
+      <c r="J97" s="20"/>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B98" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F98" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G98" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H98" s="19"/>
+      <c r="I98" s="19"/>
+      <c r="J98" s="20"/>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B99" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F99" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G99" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H99" s="19"/>
+      <c r="I99" s="19"/>
+      <c r="J99" s="20"/>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B100" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F100" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G100" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H100" s="19"/>
+      <c r="I100" s="19"/>
+      <c r="J100" s="20"/>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B101" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F101" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G101" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H101" s="19"/>
+      <c r="I101" s="19"/>
+      <c r="J101" s="20"/>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B102" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F102" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G102" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H102" s="19"/>
+      <c r="I102" s="19"/>
+      <c r="J102" s="20"/>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B103" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F103" s="24">
+        <v>31249</v>
+      </c>
+      <c r="G103" s="24">
+        <v>781242</v>
+      </c>
+      <c r="H103" s="25"/>
+      <c r="I103" s="25"/>
+      <c r="J103" s="26"/>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B108" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C108" s="32"/>
+      <c r="H108" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B109" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C109" s="32"/>
+      <c r="H109" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="H103:J103"/>
-    <mergeCell ref="H102:J102"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="H109:J109"/>
+    <mergeCell ref="H108:J108"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
